--- a/fig_11_2/male.xlsx
+++ b/fig_11_2/male.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,169 +417,169 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Locus</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sentence_length</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>fraction_sentence_relative</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>relative_clause_length</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>alius</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>antequam</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>atque_consonant</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>conjunction</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cum_clause</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>demonstrative</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>dum</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>gerundive</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>idem</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>interrogative</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>ipse</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>iste</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>o_interjection</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>preposition</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>priusquam</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>quidam</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>quin</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>quominus</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>reflexive</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>superlative</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ut</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Speaker</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Addressee</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Human/Divine</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Male/Female</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -700,7 +688,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -809,7 +797,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -918,7 +906,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1027,7 +1015,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1136,7 +1124,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1243,7 +1231,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>10</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1352,7 +1340,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>11</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1461,7 +1449,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>20</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1570,7 +1558,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>21</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1679,7 +1667,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>23</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1788,7 +1776,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>24</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1895,7 +1883,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>25</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -2004,7 +1992,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>27</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -2111,7 +2099,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>28</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -2220,7 +2208,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>31</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -2329,7 +2317,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>33</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -2438,7 +2426,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>36</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -2547,7 +2535,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>39</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2656,7 +2644,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>40</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2765,7 +2753,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>41</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2874,7 +2862,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>47</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2983,7 +2971,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>48</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -3092,7 +3080,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>50</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -3201,7 +3189,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>55</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -3308,7 +3296,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>57</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -3417,7 +3405,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>77</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -3524,7 +3512,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>83</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -3633,7 +3621,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>85</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -3742,7 +3730,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>91</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -3849,7 +3837,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>92</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -3958,7 +3946,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>93</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -4067,7 +4055,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>94</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>95</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -4283,7 +4271,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>98</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -4392,7 +4380,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>100</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -4501,7 +4489,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>101</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -4608,7 +4596,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>104</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -4715,7 +4703,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>105</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -4824,7 +4812,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>106</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -4933,7 +4921,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>107</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -5042,7 +5030,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>108</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -5149,7 +5137,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>112</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -5258,7 +5246,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>115</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -5367,7 +5355,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>116</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -5476,7 +5464,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>117</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -5585,7 +5573,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>124</v>
       </c>
       <c r="B48" t="inlineStr">
